--- a/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,86; -15,06</t>
+          <t>-43,03; -15,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -16,19</t>
+          <t>-44,98; -18,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-47,41; -8,44</t>
+          <t>-49,0; -10,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 1,36</t>
+          <t>-25,34; 0,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 8,46</t>
+          <t>-18,32; 8,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -6,46</t>
+          <t>-34,22; -5,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,2; -10,87</t>
+          <t>-30,39; -11,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,44; -8,53</t>
+          <t>-26,19; -7,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,43; -14,3</t>
+          <t>-37,38; -14,04</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,6; -40,8</t>
+          <t>-83,02; -40,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,42; -45,48</t>
+          <t>-85,83; -50,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,73</t>
+          <t>-100,0; -14,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,24; 8,5</t>
+          <t>-74,49; 9,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 46,06</t>
+          <t>-54,34; 42,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,65</t>
+          <t>-100,0; 16,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-73,92; -34,01</t>
+          <t>-75,06; -36,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,87; -27,1</t>
+          <t>-65,71; -24,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-93,68; -35,94</t>
+          <t>-94,3; -39,19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 8,78</t>
+          <t>-7,25; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 7,23</t>
+          <t>-8,67; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 22,62</t>
+          <t>-9,33; 22,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 3,48</t>
+          <t>-11,82; 2,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 8,29</t>
+          <t>-8,26; 7,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 12,35</t>
+          <t>-14,48; 9,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 4,15</t>
+          <t>-6,95; 3,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 4,84</t>
+          <t>-6,33; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 11,06</t>
+          <t>-8,57; 9,53</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 103,07</t>
+          <t>-43,95; 99,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 91,59</t>
+          <t>-55,37; 76,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,48; 210,1</t>
+          <t>-74,36; 233,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 35,53</t>
+          <t>-62,92; 25,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 73,87</t>
+          <t>-43,91; 71,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,77; 103,16</t>
+          <t>-78,89; 85,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 37,79</t>
+          <t>-42,9; 32,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 44,75</t>
+          <t>-37,93; 44,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 89,82</t>
+          <t>-56,82; 78,11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 15,69</t>
+          <t>-9,21; 15,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 10,72</t>
+          <t>-12,25; 11,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 0,13</t>
+          <t>-25,42; 3,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 5,97</t>
+          <t>-15,71; 5,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,02; -3,26</t>
+          <t>-23,46; -4,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 5,63</t>
+          <t>-23,8; 6,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 7,38</t>
+          <t>-8,85; 7,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 1,09</t>
+          <t>-14,86; 0,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -2,86</t>
+          <t>-20,85; -1,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 113,65</t>
+          <t>-32,35; 118,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 85,74</t>
+          <t>-48,26; 84,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,38</t>
+          <t>-100,0; 91,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,01; 39,17</t>
+          <t>-54,37; 35,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -13,62</t>
+          <t>-85,59; -17,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,85; 41,21</t>
+          <t>-91,51; 52,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 42,95</t>
+          <t>-35,59; 41,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 7,92</t>
+          <t>-58,16; 2,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-89,71; -7,35</t>
+          <t>-90,04; 2,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,92; 2,75</t>
+          <t>-18,73; 3,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 4,07</t>
+          <t>-17,35; 3,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 36,64</t>
+          <t>-14,44; 36,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,48; -5,25</t>
+          <t>-24,04; -6,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,48; -1,82</t>
+          <t>-22,53; -1,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 1,55</t>
+          <t>-24,69; 0,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,99; -3,59</t>
+          <t>-18,1; -4,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -0,88</t>
+          <t>-17,16; -2,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 13,05</t>
+          <t>-17,07; 13,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 17,08</t>
+          <t>-65,53; 18,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 27,86</t>
+          <t>-59,86; 19,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 186,87</t>
+          <t>-60,45; 181,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,86; -26,69</t>
+          <t>-88,14; -33,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,32; -2,73</t>
+          <t>-78,92; -6,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,37</t>
+          <t>-100,0; 25,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-69,35; -20,17</t>
+          <t>-68,98; -21,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,35; -2,67</t>
+          <t>-63,29; -11,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-73,89; 68,0</t>
+          <t>-70,38; 72,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -1,66</t>
+          <t>-30,57; -2,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 21,19</t>
+          <t>-12,22; 21,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,97; -10,76</t>
+          <t>-35,35; -10,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 13,12</t>
+          <t>-17,88; 13,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 23,97</t>
+          <t>-9,09; 25,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,02; 37,18</t>
+          <t>-24,16; 34,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 2,3</t>
+          <t>-19,08; 1,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 18,55</t>
+          <t>-3,59; 18,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 12,53</t>
+          <t>-23,5; 15,08</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-93,51; 3,25</t>
+          <t>-93,66; 2,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 166,49</t>
+          <t>-39,96; 178,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,39 +1662,39 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,14; 95,09</t>
+          <t>-59,8; 117,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 182,84</t>
+          <t>-32,69; 200,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,33</t>
+          <t>-100,0; 243,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-65,88; 14,65</t>
+          <t>-68,25; 16,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 123,18</t>
+          <t>-13,35; 119,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,81</t>
+          <t>-100,0; 91,47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 18,95</t>
+          <t>-8,19; 19,61</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 5,41</t>
+          <t>-17,24; 5,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 4,58</t>
+          <t>-24,67; 5,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 7,53</t>
+          <t>-15,41; 8,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 5,84</t>
+          <t>-17,17; 4,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 15,4</t>
+          <t>-16,93; 16,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 9,95</t>
+          <t>-7,24; 9,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 2,09</t>
+          <t>-14,56; 1,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,8; 6,94</t>
+          <t>-16,38; 6,84</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 140,73</t>
+          <t>-31,49; 132,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,92; 40,31</t>
+          <t>-65,56; 46,53</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,99</t>
+          <t>-100,0; 50,96</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,58; 59,05</t>
+          <t>-60,79; 74,44</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-69,86; 55,43</t>
+          <t>-66,5; 43,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-73,1; 115,28</t>
+          <t>-75,29; 131,8</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 68,8</t>
+          <t>-30,01; 66,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 13,51</t>
+          <t>-59,42; 15,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-74,06; 51,22</t>
+          <t>-71,96; 47,08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 8,7</t>
+          <t>-8,46; 9,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 7,81</t>
+          <t>-11,12; 6,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 8,59</t>
+          <t>-21,63; 10,93</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 11,64</t>
+          <t>-5,63; 11,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 15,56</t>
+          <t>-3,52; 15,19</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 16,24</t>
+          <t>-13,85; 16,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 7,56</t>
+          <t>-4,81; 7,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,81</t>
+          <t>-4,41; 9,05</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 8,24</t>
+          <t>-15,49; 6,47</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 39,35</t>
+          <t>-26,49; 42,39</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 34,52</t>
+          <t>-34,92; 29,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-74,67; 38,35</t>
+          <t>-75,14; 48,74</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 62,77</t>
+          <t>-20,72; 67,54</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 85,58</t>
+          <t>-12,68; 83,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,22; 82,41</t>
+          <t>-55,98; 82,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 35,72</t>
+          <t>-16,84; 36,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 41,08</t>
+          <t>-16,22; 41,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 37,95</t>
+          <t>-57,59; 29,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 11,6</t>
+          <t>-4,8; 11,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 6,42</t>
+          <t>-10,13; 6,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6,55; 51,38</t>
+          <t>4,96; 51,08</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,15; 16,29</t>
+          <t>1,1; 16,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,01</t>
+          <t>-2,65; 12,16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,53; 51,94</t>
+          <t>12,03; 50,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,67; 12,56</t>
+          <t>1,12; 12,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 7,62</t>
+          <t>-4,12; 6,94</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>14,03; 43,29</t>
+          <t>16,17; 43,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,24; 62,43</t>
+          <t>-17,43; 66,82</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 33,71</t>
+          <t>-37,12; 37,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20,56; 249,32</t>
+          <t>19,68; 261,47</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3,99; 110,31</t>
+          <t>4,76; 115,21</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 81,07</t>
+          <t>-12,66; 84,17</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>61,82; 340,59</t>
+          <t>58,94; 328,08</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,01; 76,1</t>
+          <t>5,31; 73,37</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 44,42</t>
+          <t>-18,18; 38,61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>69,41; 238,34</t>
+          <t>72,76; 234,47</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,51</t>
+          <t>-6,34; 1,68</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,95</t>
+          <t>-8,35; -0,78</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 3,36</t>
+          <t>-10,55; 3,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,19</t>
+          <t>-5,35; 2,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,68</t>
+          <t>-4,39; 2,67</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,89</t>
+          <t>-6,73; 5,55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,84</t>
+          <t>-4,51; 1,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,02</t>
+          <t>-5,04; 0,19</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,2</t>
+          <t>-7,02; 2,15</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 7,67</t>
+          <t>-24,08; 8,58</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -4,29</t>
+          <t>-32,78; -3,46</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 14,95</t>
+          <t>-43,12; 14,82</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 12,28</t>
+          <t>-24,57; 11,46</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 14,48</t>
+          <t>-20,25; 14,37</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 30,88</t>
+          <t>-31,11; 29,31</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 3,98</t>
+          <t>-19,19; 5,45</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 0,11</t>
+          <t>-21,51; 1,04</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 10,65</t>
+          <t>-31,52; 10,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,03; -15,34</t>
+          <t>-42,84; -16,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-44,98; -18,92</t>
+          <t>-43,16; -18,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -10,82</t>
+          <t>-47,89; -6,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,34; 0,93</t>
+          <t>-25,08; 1,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 8,25</t>
+          <t>-18,49; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -5,69</t>
+          <t>-34,1; -7,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,39; -11,36</t>
+          <t>-30,85; -12,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,19; -7,36</t>
+          <t>-27,08; -8,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,38; -14,04</t>
+          <t>-37,6; -15,31</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,02; -40,89</t>
+          <t>-83,5; -42,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,83; -50,43</t>
+          <t>-83,86; -46,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -14,57</t>
+          <t>-100,0; -6,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 9,74</t>
+          <t>-73,5; 10,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,34; 42,93</t>
+          <t>-54,37; 50,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,79</t>
+          <t>-100,0; -11,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,06; -36,87</t>
+          <t>-75,77; -39,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,71; -24,38</t>
+          <t>-66,47; -25,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,3; -39,19</t>
+          <t>-94,03; -38,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 8,7</t>
+          <t>-6,42; 9,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 6,67</t>
+          <t>-8,9; 7,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 22,07</t>
+          <t>-9,9; 21,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 2,72</t>
+          <t>-12,64; 2,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 7,86</t>
+          <t>-8,2; 8,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 9,81</t>
+          <t>-12,74; 13,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 3,65</t>
+          <t>-7,12; 3,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 4,8</t>
+          <t>-5,68; 5,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 9,53</t>
+          <t>-9,01; 9,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 99,84</t>
+          <t>-40,88; 114,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 76,27</t>
+          <t>-53,88; 89,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,36; 233,6</t>
+          <t>-76,7; 245,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-62,92; 25,22</t>
+          <t>-65,05; 26,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 71,55</t>
+          <t>-42,76; 71,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,89; 85,97</t>
+          <t>-71,76; 106,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 32,83</t>
+          <t>-43,69; 36,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 44,18</t>
+          <t>-36,04; 53,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,82; 78,11</t>
+          <t>-59,75; 74,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 15,6</t>
+          <t>-7,17; 15,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 11,64</t>
+          <t>-12,25; 11,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 3,02</t>
+          <t>-25,14; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 5,48</t>
+          <t>-14,69; 7,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,46; -4,25</t>
+          <t>-23,22; -3,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,8; 6,17</t>
+          <t>-23,12; 7,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 7,27</t>
+          <t>-8,6; 7,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 0,33</t>
+          <t>-14,49; 0,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,85; -1,16</t>
+          <t>-21,66; -2,12</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 118,75</t>
+          <t>-27,91; 119,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 84,51</t>
+          <t>-49,07; 80,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,64</t>
+          <t>-100,0; 76,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 35,47</t>
+          <t>-54,98; 47,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,59; -17,81</t>
+          <t>-83,33; -17,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,51; 52,18</t>
+          <t>-89,43; 55,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 41,6</t>
+          <t>-34,07; 43,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 2,23</t>
+          <t>-57,77; 3,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,04; 2,16</t>
+          <t>-90,05; -5,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 3,0</t>
+          <t>-19,59; 2,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 3,62</t>
+          <t>-18,15; 5,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 36,83</t>
+          <t>-12,63; 36,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,04; -6,02</t>
+          <t>-23,88; -5,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,53; -1,36</t>
+          <t>-20,56; -1,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 0,54</t>
+          <t>-24,28; 2,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,1; -4,28</t>
+          <t>-18,53; -4,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-17,16; -2,57</t>
+          <t>-16,07; -1,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 13,3</t>
+          <t>-16,03; 14,6</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 18,35</t>
+          <t>-65,56; 14,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-59,86; 19,98</t>
+          <t>-61,97; 29,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,45; 181,09</t>
+          <t>-52,29; 200,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-88,14; -33,3</t>
+          <t>-86,14; -28,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,92; -6,46</t>
+          <t>-77,86; -4,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 25,42</t>
+          <t>-100,0; 27,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -21,48</t>
+          <t>-70,36; -22,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-63,29; -11,67</t>
+          <t>-60,64; -6,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,38; 72,5</t>
+          <t>-68,14; 74,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-30,57; -2,69</t>
+          <t>-31,66; -4,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 21,25</t>
+          <t>-10,2; 21,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-35,35; -10,57</t>
+          <t>-36,77; -12,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 13,89</t>
+          <t>-17,36; 15,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,09; 25,07</t>
+          <t>-7,83; 23,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 34,73</t>
+          <t>-23,84; 34,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-19,08; 1,53</t>
+          <t>-18,54; 2,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 18,36</t>
+          <t>-5,72; 18,92</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 15,08</t>
+          <t>-24,01; 11,35</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-93,66; 2,86</t>
+          <t>-96,81; -5,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,96; 178,25</t>
+          <t>-37,26; 164,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,8; 117,15</t>
+          <t>-57,28; 127,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 200,68</t>
+          <t>-29,18; 175,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 243,34</t>
+          <t>-100,0; 242,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-68,25; 16,83</t>
+          <t>-65,43; 19,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 119,78</t>
+          <t>-18,62; 123,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,47</t>
+          <t>-100,0; 69,76</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 19,61</t>
+          <t>-7,57; 19,62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 5,57</t>
+          <t>-18,64; 6,5</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 5,13</t>
+          <t>-24,64; 4,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 8,58</t>
+          <t>-15,63; 8,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 4,78</t>
+          <t>-16,76; 4,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 16,64</t>
+          <t>-15,92; 14,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 9,89</t>
+          <t>-8,05; 9,74</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 1,97</t>
+          <t>-14,45; 2,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 6,84</t>
+          <t>-16,44; 7,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 132,73</t>
+          <t>-30,0; 141,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-65,56; 46,53</t>
+          <t>-66,65; 49,66</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 50,96</t>
+          <t>-100,0; 55,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,79; 74,44</t>
+          <t>-64,48; 66,29</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-66,5; 43,74</t>
+          <t>-68,39; 37,45</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-75,29; 131,8</t>
+          <t>-70,64; 117,44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,01; 66,76</t>
+          <t>-32,91; 64,63</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,42; 15,06</t>
+          <t>-59,27; 20,11</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,96; 47,08</t>
+          <t>-71,45; 51,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 9,33</t>
+          <t>-9,84; 8,4</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 6,37</t>
+          <t>-11,48; 7,77</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 10,93</t>
+          <t>-21,66; 11,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 11,62</t>
+          <t>-6,14; 10,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 15,19</t>
+          <t>-2,4; 16,03</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 16,15</t>
+          <t>-16,31; 16,34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 7,91</t>
+          <t>-5,02; 7,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 9,05</t>
+          <t>-4,41; 8,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,49; 6,47</t>
+          <t>-15,29; 6,68</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 42,39</t>
+          <t>-29,65; 36,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 29,77</t>
+          <t>-36,13; 35,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-75,14; 48,74</t>
+          <t>-75,71; 45,13</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 67,54</t>
+          <t>-23,49; 59,12</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 83,37</t>
+          <t>-10,18; 91,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,98; 82,64</t>
+          <t>-64,26; 83,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 36,29</t>
+          <t>-18,4; 31,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 41,85</t>
+          <t>-16,07; 40,49</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 29,6</t>
+          <t>-57,57; 29,59</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 11,51</t>
+          <t>-4,74; 12,14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 6,85</t>
+          <t>-10,01; 6,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4,96; 51,08</t>
+          <t>6,55; 51,42</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,1; 16,62</t>
+          <t>1,29; 16,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 12,16</t>
+          <t>-2,65; 12,49</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>12,03; 50,58</t>
+          <t>13,7; 51,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,12; 12,5</t>
+          <t>0,27; 11,65</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 6,94</t>
+          <t>-3,45; 7,32</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>16,17; 43,95</t>
+          <t>15,43; 46,01</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,43; 66,82</t>
+          <t>-17,22; 65,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 37,37</t>
+          <t>-35,69; 35,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>19,68; 261,47</t>
+          <t>23,23; 258,75</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4,76; 115,21</t>
+          <t>6,05; 116,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 84,17</t>
+          <t>-12,09; 87,88</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>58,94; 328,08</t>
+          <t>69,25; 352,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,31; 73,37</t>
+          <t>1,14; 67,84</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 38,61</t>
+          <t>-14,03; 40,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>72,76; 234,47</t>
+          <t>71,9; 252,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,68</t>
+          <t>-6,25; 1,58</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,78</t>
+          <t>-7,93; 0,02</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 3,27</t>
+          <t>-10,27; 3,55</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,12</t>
+          <t>-4,87; 2,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,67</t>
+          <t>-4,45; 2,75</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,55</t>
+          <t>-6,78; 5,75</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,12</t>
+          <t>-4,4; 0,52</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,19</t>
+          <t>-4,85; 0,34</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,15</t>
+          <t>-7,78; 1,91</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 8,58</t>
+          <t>-25,09; 7,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -3,46</t>
+          <t>-31,69; -0,26</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 14,82</t>
+          <t>-42,69; 15,6</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 11,46</t>
+          <t>-22,08; 12,6</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 14,37</t>
+          <t>-20,22; 14,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,31</t>
+          <t>-31,79; 30,46</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 5,45</t>
+          <t>-19,19; 2,61</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 1,04</t>
+          <t>-20,92; 1,99</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 10,05</t>
+          <t>-35,08; 9,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-12,25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,78</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-22,07</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-29,85</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-31,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-32,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,78</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-22,4</t>
+          <t>-31,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-27,68</t>
+          <t>-27,01</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-42,84; -16,3</t>
+          <t>-25,44; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -18,22</t>
+          <t>-18,38; 8,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-47,89; -6,59</t>
+          <t>-34,47; -4,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 1,49</t>
+          <t>-42,86; -15,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 8,99</t>
+          <t>-43,88; -16,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,1; -7,36</t>
+          <t>-46,89; -6,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,85; -12,15</t>
+          <t>-30,2; -10,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,08; -8,04</t>
+          <t>-27,44; -8,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-37,6; -15,31</t>
+          <t>-37,01; -12,7</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-17,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-81,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-67,54%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-71,21%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-74,11%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,36%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-17,72%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-82,95%</t>
+          <t>-72,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-78,1%</t>
+          <t>-76,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-83,5; -42,99</t>
+          <t>-74,24; 8,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-83,86; -46,84</t>
+          <t>-54,4; 46,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,44</t>
+          <t>-100,0; 25,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,5; 10,27</t>
+          <t>-83,6; -40,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,37; 50,83</t>
+          <t>-85,42; -45,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,96</t>
+          <t>-100,0; -5,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,77; -39,25</t>
+          <t>-73,92; -34,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -25,29</t>
+          <t>-66,87; -27,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,03; -38,1</t>
+          <t>-93,21; -31,86</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,29</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,73</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,63</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>2,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,58</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 9,66</t>
+          <t>-13,13; 3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 7,33</t>
+          <t>-8,34; 8,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 21,85</t>
+          <t>-14,03; 8,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 2,66</t>
+          <t>-5,73; 8,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 8,0</t>
+          <t>-8,24; 7,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 13,74</t>
+          <t>-9,37; 23,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 3,83</t>
+          <t>-7,4; 4,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,74</t>
+          <t>-6,34; 4,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 9,7</t>
+          <t>-9,04; 9,34</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-29,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-1,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-34,16%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,82%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-6,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-29,88%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,35%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,87%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-4,2%</t>
+          <t>-11,97%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,88; 114,23</t>
+          <t>-64,23; 35,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 89,59</t>
+          <t>-42,51; 73,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-76,7; 245,25</t>
+          <t>-77,15; 82,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,05; 26,83</t>
+          <t>-39,08; 103,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 71,68</t>
+          <t>-51,96; 91,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,76; 106,19</t>
+          <t>-72,89; 220,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 36,33</t>
+          <t>-42,67; 37,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 53,56</t>
+          <t>-37,12; 44,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,75; 74,6</t>
+          <t>-60,35; 81,45</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-13,45</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-12,33</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-14,85</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-13,45</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,69</t>
+          <t>-14,8</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-13,08</t>
+          <t>-13,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 15,89</t>
+          <t>-14,99; 5,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 11,1</t>
+          <t>-23,02; -3,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 4,11</t>
+          <t>-25,39; 4,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 7,44</t>
+          <t>-8,49; 15,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,22; -3,78</t>
+          <t>-11,69; 10,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 7,84</t>
+          <t>-25,28; 0,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 7,46</t>
+          <t>-9,32; 7,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 0,3</t>
+          <t>-15,07; 1,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-21,66; -2,12</t>
+          <t>-21,97; -3,83</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-20,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-60,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-55,24%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>20,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-75,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-20,27%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-60,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-52,4%</t>
+          <t>-74,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-62,04%</t>
+          <t>-64,31%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 119,53</t>
+          <t>-54,01; 39,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 80,32</t>
+          <t>-83,52; -13,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 76,15</t>
+          <t>-92,25; 33,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 47,58</t>
+          <t>-32,48; 113,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-83,33; -17,89</t>
+          <t>-45,63; 85,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-89,43; 55,41</t>
+          <t>-100,0; 36,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 43,95</t>
+          <t>-35,73; 42,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 3,09</t>
+          <t>-58,75; 7,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-90,05; -5,46</t>
+          <t>-90,21; -10,03</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-14,07</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-10,94</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-14,73</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-8,23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-6,52</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,34</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-14,07</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-10,94</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-13,99</t>
+          <t>10,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-2,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 2,27</t>
+          <t>-23,48; -5,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 5,06</t>
+          <t>-21,48; -1,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 36,45</t>
+          <t>-25,49; -0,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,88; -5,18</t>
+          <t>-18,92; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -1,36</t>
+          <t>-17,24; 4,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 2,19</t>
+          <t>-13,59; 40,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-18,53; -4,4</t>
+          <t>-17,99; -3,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-16,07; -1,49</t>
+          <t>-16,4; -0,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 14,6</t>
+          <t>-16,28; 14,74</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-67,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-52,45%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-70,61%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-35,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-27,91%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>31,43%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-67,46%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-52,45%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-67,07%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,76%</t>
+          <t>-11,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-65,56; 14,16</t>
+          <t>-85,86; -26,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 29,56</t>
+          <t>-80,32; -2,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 200,0</t>
+          <t>-100,0; 28,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-86,14; -28,79</t>
+          <t>-64,98; 17,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,86; -4,84</t>
+          <t>-61,81; 27,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,26</t>
+          <t>-55,21; 194,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-70,36; -22,3</t>
+          <t>-69,35; -20,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,64; -6,72</t>
+          <t>-62,35; -2,67</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,14; 74,67</t>
+          <t>-69,59; 78,55</t>
         </is>
       </c>
     </row>
@@ -1488,34 +1488,34 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-1,19</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-15,75</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,27</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>-21,69</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,58</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>-8,17</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-10,16</t>
+          <t>-10,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,66; -4,23</t>
+          <t>-18,38; 13,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 21,8</t>
+          <t>-7,51; 23,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-36,77; -12,32</t>
+          <t>-24,01; 38,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 15,45</t>
+          <t>-28,49; -1,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 23,71</t>
+          <t>-10,91; 21,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 34,2</t>
+          <t>-35,97; -10,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 2,68</t>
+          <t>-18,02; 2,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 18,92</t>
+          <t>-4,99; 18,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 11,35</t>
+          <t>-23,42; 12,65</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-6,46%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>39,34%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-5,48%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-72,64%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>24,31%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-6,46%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-7,49%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>-37,56%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,71%</t>
+          <t>-47,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-96,81; -5,08</t>
+          <t>-59,14; 95,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 164,18</t>
+          <t>-26,88; 182,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 258,73</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-93,51; 3,25</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-41,62; 166,49</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-57,28; 127,6</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>-29,18; 175,28</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 242,31</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 19,3</t>
+          <t>-65,88; 14,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 123,71</t>
+          <t>-18,12; 123,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,76</t>
+          <t>-100,0; 87,83</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-3,22</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-5,8</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>5,95</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-6,03</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-11,96</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-3,22</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-5,8</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,34</t>
+          <t>-13,6</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,49</t>
+          <t>-6,86</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 19,62</t>
+          <t>-15,95; 7,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 6,5</t>
+          <t>-17,96; 5,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 4,61</t>
+          <t>-16,99; 17,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 8,3</t>
+          <t>-7,23; 18,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 4,48</t>
+          <t>-17,75; 5,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 14,23</t>
+          <t>-25,51; 0,28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 9,74</t>
+          <t>-7,33; 9,95</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 2,17</t>
+          <t>-13,85; 2,09</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 7,25</t>
+          <t>-16,64; 6,71</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-16,89%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-30,36%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-12,98%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>29,65%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-30,05%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-59,62%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-16,89%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-30,36%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-17,51%</t>
+          <t>-67,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-33,18%</t>
+          <t>-35,03%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 141,51</t>
+          <t>-64,58; 59,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,65; 49,66</t>
+          <t>-69,86; 55,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,01</t>
+          <t>-73,69; 130,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 66,29</t>
+          <t>-30,69; 140,73</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 37,45</t>
+          <t>-66,92; 40,31</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,64; 117,44</t>
+          <t>-100,0; 27,57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 64,63</t>
+          <t>-32,77; 68,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 20,11</t>
+          <t>-59,95; 13,51</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-71,45; 51,89</t>
+          <t>-74,59; 48,42</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6,29</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,44</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-0,07</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-1,94</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-8,76</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,29</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-6,13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-4,96</t>
+          <t>-3,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 8,4</t>
+          <t>-5,54; 11,64</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 7,77</t>
+          <t>-3,05; 15,56</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 11,03</t>
+          <t>-14,7; 16,04</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 10,81</t>
+          <t>-8,84; 8,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 16,03</t>
+          <t>-11,81; 7,81</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 16,34</t>
+          <t>-20,24; 13,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,03</t>
+          <t>-5,39; 7,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 8,66</t>
+          <t>-4,48; 8,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-15,29; 6,68</t>
+          <t>-13,53; 10,87</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>28,17%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-6,44%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-0,27%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-7,14%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-32,21%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>28,17%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,55%</t>
+          <t>-22,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-20,04%</t>
+          <t>-15,26%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 36,41</t>
+          <t>-22,08; 62,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-36,13; 35,15</t>
+          <t>-11,95; 85,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-75,71; 45,13</t>
+          <t>-62,1; 82,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 59,12</t>
+          <t>-28,07; 39,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 91,98</t>
+          <t>-37,02; 34,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 83,2</t>
+          <t>-69,28; 56,78</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 31,89</t>
+          <t>-19,01; 35,72</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 40,49</t>
+          <t>-15,79; 41,08</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,57; 29,59</t>
+          <t>-53,23; 48,12</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>8,98</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4,78</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>32,94</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>3,49</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-1,53</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>28,81</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>8,98</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,78</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,82</t>
+          <t>32,7</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>30,82</t>
+          <t>32,33</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 12,14</t>
+          <t>1,15; 16,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 6,62</t>
+          <t>-3,24; 12,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6,55; 51,42</t>
+          <t>12,09; 52,59</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,29; 16,37</t>
+          <t>-5,53; 11,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 12,49</t>
+          <t>-9,03; 6,42</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,7; 51,61</t>
+          <t>9,06; 54,78</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,27; 11,65</t>
+          <t>0,67; 12,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 7,32</t>
+          <t>-3,51; 7,62</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,43; 46,01</t>
+          <t>15,11; 45,06</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>49,88%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>182,99%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>15,16%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-6,65%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>125,33%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>26,56%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>182,36%</t>
+          <t>142,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>151,34%</t>
+          <t>158,74%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 65,62</t>
+          <t>3,99; 110,31</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,69; 35,91</t>
+          <t>-14,7; 81,07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>23,23; 258,75</t>
+          <t>58,76; 341,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6,05; 116,14</t>
+          <t>-20,24; 62,43</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 87,88</t>
+          <t>-33,76; 33,71</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>69,25; 352,74</t>
+          <t>29,6; 270,23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,14; 67,84</t>
+          <t>3,01; 76,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 40,88</t>
+          <t>-15,35; 44,42</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>71,9; 252,72</t>
+          <t>73,26; 248,51</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,58</t>
+          <t>-4,79; 2,19</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,02</t>
+          <t>-4,79; 2,68</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,55</t>
+          <t>-6,58; 6,74</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,36</t>
+          <t>-6,21; 1,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,75</t>
+          <t>-8,2; -0,95</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,75</t>
+          <t>-9,88; 5,4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,52</t>
+          <t>-4,18; 0,84</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,34</t>
+          <t>-4,95; 0,02</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,91</t>
+          <t>-6,5; 3,16</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-6,78%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-3,56%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-4,55%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-9,7%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-18,44%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-17,91%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-6,78%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-3,56%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-6,17%</t>
+          <t>-12,56%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-12,37%</t>
+          <t>-9,0%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 7,44</t>
+          <t>-21,79; 12,28</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -0,26</t>
+          <t>-21,19; 14,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 15,6</t>
+          <t>-31,55; 34,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 12,6</t>
+          <t>-24,46; 7,67</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 14,85</t>
+          <t>-32,55; -4,29</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 30,46</t>
+          <t>-41,72; 24,5</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 2,61</t>
+          <t>-18,57; 3,98</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 1,99</t>
+          <t>-21,49; 0,11</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 9,53</t>
+          <t>-28,89; 15,63</t>
         </is>
       </c>
     </row>
